--- a/EL MIRADOR/Septiembre/Septiembre - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Septiembre/Septiembre - EL MIRADOR .xlsx
@@ -5,29 +5,34 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA669BD5-900D-4633-938C-56E78228B442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF0C658-27AD-462C-B657-9225E941B6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
+    <sheet name="SUELDOS" sheetId="5" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$149</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$149</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SUELDOS!$A$3:$J$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="354">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1088,6 +1093,15 @@
   </si>
   <si>
     <t>Heredia, Christian</t>
+  </si>
+  <si>
+    <t>Firma</t>
+  </si>
+  <si>
+    <t>__________________________________</t>
+  </si>
+  <si>
+    <t>Aclaracion</t>
   </si>
 </sst>
 </file>
@@ -1696,7 +1710,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1974,14 +1988,26 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2016,19 +2042,34 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2165,6 +2206,39 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="RESUMEN"/>
+      <sheetName val="PRORRATEO"/>
+      <sheetName val="ANOTACIONES"/>
+      <sheetName val="SUELDOS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="22">
+          <cell r="A22" t="str">
+            <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Sueldo encargada Miriam</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2455,24 +2529,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="126"/>
       <c r="B1" s="135"/>
       <c r="C1" s="145" t="s">
@@ -2486,7 +2560,7 @@
       <c r="I1" s="124"/>
       <c r="J1" s="125"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="127"/>
       <c r="B2" s="136"/>
       <c r="C2" s="136" t="s">
@@ -2500,7 +2574,7 @@
       <c r="I2" s="137"/>
       <c r="J2" s="123"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="127"/>
       <c r="B3" s="136"/>
       <c r="C3" s="136" t="s">
@@ -2516,7 +2590,7 @@
       <c r="I3" s="137"/>
       <c r="J3" s="123"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="127"/>
       <c r="B4" s="136"/>
       <c r="C4" s="136" t="s">
@@ -2530,7 +2604,7 @@
       <c r="I4" s="137"/>
       <c r="J4" s="123"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="131"/>
       <c r="B5" s="136"/>
       <c r="C5" s="136" t="s">
@@ -2546,7 +2620,7 @@
       <c r="I5" s="136"/>
       <c r="J5" s="132"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="131"/>
       <c r="B6" s="136"/>
       <c r="C6" s="136" t="s">
@@ -2560,7 +2634,7 @@
       <c r="I6" s="136"/>
       <c r="J6" s="132"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="133"/>
       <c r="B7" s="134"/>
       <c r="C7" s="134"/>
@@ -2572,11 +2646,11 @@
       <c r="I7" s="134"/>
       <c r="J7" s="138"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="193" t="s">
         <v>265</v>
       </c>
@@ -2590,7 +2664,7 @@
       <c r="I14" s="193"/>
       <c r="J14" s="193"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="193"/>
       <c r="B15" s="193"/>
       <c r="C15" s="193"/>
@@ -2602,7 +2676,7 @@
       <c r="I15" s="193"/>
       <c r="J15" s="193"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="193"/>
       <c r="B16" s="193"/>
       <c r="C16" s="193"/>
@@ -2614,7 +2688,7 @@
       <c r="I16" s="193"/>
       <c r="J16" s="193"/>
     </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="193"/>
       <c r="B17" s="193"/>
       <c r="C17" s="193"/>
@@ -2626,7 +2700,7 @@
       <c r="I17" s="193"/>
       <c r="J17" s="193"/>
     </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="193"/>
       <c r="B18" s="193"/>
       <c r="C18" s="193"/>
@@ -2638,11 +2712,11 @@
       <c r="I18" s="193"/>
       <c r="J18" s="193"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="108"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="202" t="s">
         <v>315</v>
       </c>
@@ -2656,7 +2730,7 @@
       <c r="I20" s="202"/>
       <c r="J20" s="202"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="202"/>
       <c r="B21" s="202"/>
       <c r="C21" s="202"/>
@@ -2668,7 +2742,7 @@
       <c r="I21" s="202"/>
       <c r="J21" s="202"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="202"/>
       <c r="B22" s="202"/>
       <c r="C22" s="202"/>
@@ -2680,10 +2754,10 @@
       <c r="I22" s="202"/>
       <c r="J22" s="202"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="108"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>19</v>
       </c>
@@ -2709,7 +2783,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
         <v>238</v>
       </c>
@@ -2723,7 +2797,7 @@
       <c r="I25" s="109"/>
       <c r="J25" s="109"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
@@ -2739,7 +2813,7 @@
       <c r="I26" s="62"/>
       <c r="J26" s="62"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>241</v>
       </c>
@@ -2755,7 +2829,7 @@
       <c r="I27" s="62"/>
       <c r="J27" s="62"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>239</v>
       </c>
@@ -2772,7 +2846,7 @@
       <c r="I28" s="62"/>
       <c r="J28" s="62"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>240</v>
       </c>
@@ -2788,7 +2862,7 @@
       <c r="I29" s="62"/>
       <c r="J29" s="62"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>331</v>
       </c>
@@ -2804,7 +2878,7 @@
       <c r="I30" s="62"/>
       <c r="J30" s="62"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>242</v>
       </c>
@@ -2820,7 +2894,7 @@
       <c r="I31" s="62"/>
       <c r="J31" s="62"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="107" t="s">
         <v>171</v>
       </c>
@@ -2837,7 +2911,7 @@
       <c r="I32" s="106"/>
       <c r="J32" s="106"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="51" t="s">
         <v>237</v>
       </c>
@@ -2851,7 +2925,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
@@ -2867,7 +2941,7 @@
       <c r="I34" s="62"/>
       <c r="J34" s="62"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>314</v>
       </c>
@@ -2881,7 +2955,7 @@
       <c r="I35" s="62"/>
       <c r="J35" s="62"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>241</v>
       </c>
@@ -2898,7 +2972,7 @@
       <c r="I36" s="62"/>
       <c r="J36" s="62"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>239</v>
       </c>
@@ -2915,7 +2989,7 @@
       <c r="I37" s="62"/>
       <c r="J37" s="62"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>240</v>
       </c>
@@ -2932,7 +3006,7 @@
       <c r="I38" s="62"/>
       <c r="J38" s="62"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>331</v>
       </c>
@@ -2948,7 +3022,7 @@
       <c r="I39" s="62"/>
       <c r="J39" s="62"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>242</v>
       </c>
@@ -2964,7 +3038,7 @@
       <c r="I40" s="62"/>
       <c r="J40" s="62"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="107" t="s">
         <v>171</v>
       </c>
@@ -2981,7 +3055,7 @@
       <c r="I41" s="106"/>
       <c r="J41" s="106"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="34" t="s">
         <v>1</v>
       </c>
@@ -3024,7 +3098,7 @@
         <v>1488737.4</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>34</v>
       </c>
@@ -3047,7 +3121,7 @@
       </c>
       <c r="L43" s="73"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3068,7 +3142,7 @@
       </c>
       <c r="L44" s="73"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="33"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3081,7 +3155,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="73"/>
     </row>
-    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -3094,7 +3168,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="73"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>40</v>
       </c>
@@ -3125,7 +3199,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>253</v>
       </c>
@@ -3146,7 +3220,7 @@
       </c>
       <c r="L48" s="73"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3162,7 +3236,7 @@
       <c r="J49" s="62"/>
       <c r="L49" s="73"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3178,7 +3252,7 @@
       <c r="J50" s="62"/>
       <c r="L50" s="73"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="33"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3197,7 +3271,7 @@
       </c>
       <c r="L51" s="73"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="34" t="s">
         <v>35</v>
       </c>
@@ -3225,7 +3299,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
         <v>247</v>
       </c>
@@ -3240,7 +3314,7 @@
       <c r="J53" s="50"/>
       <c r="L53" s="73"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="36" t="s">
         <v>250</v>
       </c>
@@ -3257,7 +3331,7 @@
       <c r="J54" s="50"/>
       <c r="L54" s="73"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>252</v>
       </c>
@@ -3276,7 +3350,7 @@
       <c r="J55" s="50"/>
       <c r="L55" s="73"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="36" t="s">
         <v>251</v>
       </c>
@@ -3296,7 +3370,7 @@
       <c r="J56" s="50"/>
       <c r="L56" s="73"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="34" t="s">
         <v>249</v>
       </c>
@@ -3339,7 +3413,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="33" t="s">
         <v>2</v>
       </c>
@@ -3354,7 +3428,7 @@
       <c r="J58" s="6"/>
       <c r="L58" s="73"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>243</v>
       </c>
@@ -3373,7 +3447,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="73"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>298</v>
       </c>
@@ -3392,7 +3466,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="73"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="34" t="s">
         <v>248</v>
       </c>
@@ -3435,7 +3509,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="33" t="s">
         <v>230</v>
       </c>
@@ -3450,7 +3524,7 @@
       <c r="J62" s="37"/>
       <c r="L62" s="73"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>234</v>
       </c>
@@ -3491,7 +3565,7 @@
       </c>
       <c r="L63" s="73"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>235</v>
       </c>
@@ -3532,7 +3606,7 @@
       </c>
       <c r="L64" s="73"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>236</v>
       </c>
@@ -3573,7 +3647,7 @@
       </c>
       <c r="L65" s="73"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="34" t="s">
         <v>3</v>
       </c>
@@ -3616,7 +3690,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>4</v>
       </c>
@@ -3631,7 +3705,7 @@
       <c r="J67" s="6"/>
       <c r="L67" s="73"/>
     </row>
-    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="78" t="s">
         <v>244</v>
       </c>
@@ -3681,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>245</v>
       </c>
@@ -3733,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>246</v>
       </c>
@@ -3770,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>317</v>
       </c>
@@ -3801,7 +3875,7 @@
       <c r="M71" s="94"/>
       <c r="N71" s="94"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="36" t="s">
         <v>301</v>
       </c>
@@ -3838,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="36" t="s">
         <v>334</v>
       </c>
@@ -3867,7 +3941,7 @@
       <c r="M73" s="94"/>
       <c r="N73" s="94"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="36" t="s">
         <v>282</v>
       </c>
@@ -3919,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="36" t="s">
         <v>283</v>
       </c>
@@ -3972,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="168" t="s">
         <v>281</v>
       </c>
@@ -4009,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="168" t="s">
         <v>324</v>
       </c>
@@ -4041,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="200" t="s">
         <v>333</v>
       </c>
@@ -4073,7 +4147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="200" t="s">
         <v>344</v>
       </c>
@@ -4105,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="164" t="s">
         <v>345</v>
       </c>
@@ -4137,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="152" t="s">
         <v>323</v>
       </c>
@@ -4172,7 +4246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="78"/>
       <c r="B82" s="79"/>
       <c r="C82" s="79"/>
@@ -4190,7 +4264,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="34" t="s">
         <v>5</v>
       </c>
@@ -4237,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -4250,7 +4324,7 @@
       <c r="J84" s="6"/>
       <c r="L84" s="73"/>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4263,7 +4337,7 @@
       <c r="J85" s="6"/>
       <c r="L85" s="73"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="33" t="s">
         <v>231</v>
       </c>
@@ -4278,7 +4352,7 @@
       <c r="J86" s="6"/>
       <c r="L86" s="73"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>318</v>
       </c>
@@ -4314,7 +4388,7 @@
       <c r="K87" s="81"/>
       <c r="L87" s="73"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>328</v>
       </c>
@@ -4335,7 +4409,7 @@
       <c r="K88" s="81"/>
       <c r="L88" s="73"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="36"/>
       <c r="C89" s="6"/>
@@ -4349,7 +4423,7 @@
       <c r="K89" s="81"/>
       <c r="L89" s="73"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="36"/>
       <c r="C90" s="6"/>
@@ -4363,7 +4437,7 @@
       <c r="K90" s="81"/>
       <c r="L90" s="73"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="36"/>
       <c r="C91" s="6"/>
@@ -4377,7 +4451,7 @@
       <c r="K91" s="81"/>
       <c r="L91" s="73"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -4391,7 +4465,7 @@
       <c r="L92" s="73"/>
       <c r="M92" s="44"/>
     </row>
-    <row r="93" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="34" t="s">
         <v>232</v>
       </c>
@@ -4435,7 +4509,7 @@
       </c>
       <c r="N93" s="44"/>
     </row>
-    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -4448,7 +4522,7 @@
       <c r="J94" s="6"/>
       <c r="L94" s="73"/>
     </row>
-    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4461,7 +4535,7 @@
       <c r="J95" s="6"/>
       <c r="L95" s="73"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>6</v>
       </c>
@@ -4476,7 +4550,7 @@
       <c r="J96" s="6"/>
       <c r="L96" s="73"/>
     </row>
-    <row r="97" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>7</v>
       </c>
@@ -4513,7 +4587,7 @@
       </c>
       <c r="L97" s="73"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="33"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4527,7 +4601,7 @@
       <c r="L98" s="73"/>
       <c r="N98" s="45"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -4541,7 +4615,7 @@
       <c r="L99" s="73"/>
       <c r="N99" s="44"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="34" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4659,7 @@
       </c>
       <c r="N100" s="44"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>28</v>
       </c>
@@ -4620,7 +4694,7 @@
       </c>
       <c r="L101" s="73"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>29</v>
       </c>
@@ -4655,7 +4729,7 @@
       </c>
       <c r="L102" s="73"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="34" t="s">
         <v>233</v>
       </c>
@@ -4698,7 +4772,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="112"/>
       <c r="B104" s="112"/>
       <c r="C104" s="112"/>
@@ -4711,7 +4785,7 @@
       <c r="J104" s="112"/>
       <c r="L104" s="73"/>
     </row>
-    <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="114" t="s">
         <v>46</v>
       </c>
@@ -4751,7 +4825,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="117"/>
       <c r="B106" s="118"/>
       <c r="C106" s="118"/>
@@ -4765,7 +4839,7 @@
       <c r="K106" s="44"/>
       <c r="L106" s="73"/>
     </row>
-    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>30</v>
       </c>
@@ -4812,7 +4886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D108" s="97"/>
       <c r="E108" s="44"/>
       <c r="F108" s="44"/>
@@ -4820,7 +4894,7 @@
       <c r="H108" s="44"/>
       <c r="I108" s="44"/>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="68" t="s">
         <v>41</v>
       </c>
@@ -4832,7 +4906,7 @@
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="C110" s="144"/>
       <c r="E110" s="44"/>
@@ -4841,7 +4915,7 @@
       <c r="H110" s="44"/>
       <c r="I110" s="44"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="C111" s="144"/>
       <c r="E111" s="44"/>
@@ -4850,7 +4924,7 @@
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="C112" s="144"/>
       <c r="E112" s="44"/>
@@ -4859,7 +4933,7 @@
       <c r="H112" s="44"/>
       <c r="I112" s="44"/>
     </row>
-    <row r="113" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="C113" s="144"/>
       <c r="E113" s="44"/>
@@ -4868,7 +4942,7 @@
       <c r="H113" s="44"/>
       <c r="I113" s="44"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="69" t="s">
         <v>17</v>
       </c>
@@ -4883,21 +4957,21 @@
       <c r="H114" s="44"/>
       <c r="I114" s="44"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E115" s="44"/>
       <c r="F115" s="44"/>
       <c r="G115" s="44"/>
       <c r="H115" s="44"/>
       <c r="I115" s="44"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E116" s="64"/>
       <c r="F116" s="64"/>
       <c r="G116" s="64"/>
       <c r="H116" s="64"/>
       <c r="I116" s="64"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="198" t="s">
         <v>36</v>
       </c>
@@ -4923,7 +4997,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="200"/>
       <c r="B118" s="201"/>
       <c r="C118" s="91"/>
@@ -4938,7 +5012,7 @@
       <c r="I118" s="72"/>
       <c r="J118" s="62"/>
     </row>
-    <row r="119" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="200"/>
       <c r="B119" s="201"/>
       <c r="C119" s="91"/>
@@ -4950,7 +5024,7 @@
       <c r="I119" s="72"/>
       <c r="J119" s="62"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="195" t="s">
         <v>17</v>
       </c>
@@ -4981,14 +5055,14 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="44"/>
       <c r="F122" s="44"/>
       <c r="G122" s="44"/>
       <c r="H122" s="44"/>
       <c r="I122" s="44"/>
     </row>
-    <row r="123" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="39" t="s">
         <v>31</v>
       </c>
@@ -4997,7 +5071,7 @@
         <v>10364214.639999999</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="41" t="s">
         <v>33</v>
       </c>
@@ -5014,7 +5088,7 @@
       <c r="H124" s="204"/>
       <c r="I124" s="204"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D125" s="204"/>
       <c r="E125" s="204"/>
       <c r="F125" s="204"/>
@@ -5022,7 +5096,7 @@
       <c r="H125" s="204"/>
       <c r="I125" s="204"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="17" t="s">
         <v>20</v>
       </c>
@@ -5035,7 +5109,7 @@
       <c r="H126" s="204"/>
       <c r="I126" s="204"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="20" t="s">
         <v>21</v>
       </c>
@@ -5050,7 +5124,7 @@
       <c r="H127" s="204"/>
       <c r="I127" s="204"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>22</v>
       </c>
@@ -5068,7 +5142,7 @@
       <c r="H128" s="204"/>
       <c r="I128" s="204"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="22" t="s">
         <v>38</v>
       </c>
@@ -5085,7 +5159,7 @@
       <c r="I129" s="204"/>
       <c r="K129" s="45"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>37</v>
       </c>
@@ -5102,7 +5176,7 @@
       <c r="I130" s="204"/>
       <c r="K130" s="55"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>313</v>
       </c>
@@ -5119,7 +5193,7 @@
       <c r="I131" s="204"/>
       <c r="K131" s="55"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>32</v>
       </c>
@@ -5135,7 +5209,7 @@
       <c r="H132" s="204"/>
       <c r="I132" s="204"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>311</v>
       </c>
@@ -5150,7 +5224,7 @@
       <c r="H133" s="204"/>
       <c r="I133" s="204"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>41</v>
       </c>
@@ -5166,7 +5240,7 @@
       <c r="H134" s="204"/>
       <c r="I134" s="204"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="22"/>
       <c r="B135" s="18"/>
       <c r="C135" s="23"/>
@@ -5177,7 +5251,7 @@
       <c r="H135" s="204"/>
       <c r="I135" s="204"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="20" t="s">
         <v>24</v>
       </c>
@@ -5193,7 +5267,7 @@
       <c r="H136" s="204"/>
       <c r="I136" s="204"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="23"/>
       <c r="C137" s="19"/>
       <c r="D137" s="204"/>
@@ -5203,7 +5277,7 @@
       <c r="H137" s="204"/>
       <c r="I137" s="204"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="17" t="s">
         <v>312</v>
       </c>
@@ -5216,7 +5290,7 @@
       <c r="H138" s="204"/>
       <c r="I138" s="204"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="20" t="s">
         <v>342</v>
       </c>
@@ -5226,13 +5300,13 @@
       <c r="C139" s="19"/>
       <c r="D139" s="26"/>
     </row>
-    <row r="140" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="191"/>
       <c r="B140" s="31"/>
       <c r="C140" s="19"/>
       <c r="D140" s="26"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="37" t="s">
         <v>17</v>
       </c>
@@ -5243,17 +5317,17 @@
       <c r="C141" s="19"/>
       <c r="D141" s="26"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="23"/>
       <c r="C142" s="19"/>
       <c r="D142" s="26"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="23"/>
       <c r="C143" s="19"/>
       <c r="D143" s="26"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C144" s="19"/>
       <c r="D144" s="44"/>
       <c r="E144" s="94"/>
@@ -5262,7 +5336,7 @@
       <c r="H144" s="94"/>
       <c r="I144" s="94"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" s="17" t="s">
         <v>25</v>
       </c>
@@ -5278,7 +5352,7 @@
       <c r="I145" s="94"/>
       <c r="J145" s="94"/>
     </row>
-    <row r="146" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="20" t="s">
         <v>260</v>
       </c>
@@ -5291,7 +5365,7 @@
       <c r="H146" s="101"/>
       <c r="I146" s="101"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" s="20"/>
       <c r="B147" s="93"/>
       <c r="C147" s="25"/>
@@ -5301,7 +5375,7 @@
       <c r="H147" s="44"/>
       <c r="I147" s="44"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="37" t="s">
         <v>17</v>
       </c>
@@ -5311,18 +5385,18 @@
       </c>
       <c r="C148" s="25"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C149" s="26"/>
       <c r="D149" s="94"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B150" s="23"/>
       <c r="C150" s="19"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R152" s="10"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B155" s="194"/>
       <c r="C155" s="194"/>
       <c r="D155" s="194"/>
@@ -5332,7 +5406,7 @@
       <c r="H155" s="103"/>
       <c r="I155" s="103"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B156" s="194"/>
       <c r="C156" s="194"/>
       <c r="D156" s="194"/>
@@ -5342,7 +5416,7 @@
       <c r="H156" s="103"/>
       <c r="I156" s="103"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B157" s="194"/>
       <c r="C157" s="194"/>
       <c r="D157" s="194"/>
@@ -5352,7 +5426,7 @@
       <c r="H157" s="103"/>
       <c r="I157" s="103"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B158" s="194"/>
       <c r="C158" s="194"/>
       <c r="D158" s="194"/>
@@ -5362,7 +5436,7 @@
       <c r="H158" s="103"/>
       <c r="I158" s="103"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B159" s="194"/>
       <c r="C159" s="194"/>
       <c r="D159" s="194"/>
@@ -5394,27 +5468,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.44140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5430,15 +5504,15 @@
       <c r="K1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="210">
+      <c r="L1" s="214">
         <f>RESUMEN!D107-RESUMEN!D105</f>
         <v>10364214.639999999</v>
       </c>
-      <c r="M1" s="211"/>
+      <c r="M1" s="215"/>
       <c r="N1" s="75"/>
       <c r="O1" s="63"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5461,7 +5535,7 @@
       <c r="N2" s="76"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: SEPTIEMBRE</v>
@@ -5483,7 +5557,7 @@
       <c r="N3" s="74"/>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5506,79 +5580,79 @@
         <v>494947.15715999901</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="206" t="s">
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="219" t="s">
+      <c r="B5" s="207" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="205" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="221" t="s">
+      <c r="D5" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="221" t="s">
+      <c r="E5" s="209" t="s">
         <v>274</v>
       </c>
-      <c r="F5" s="206" t="s">
+      <c r="F5" s="205" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="206" t="s">
+      <c r="G5" s="205" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="206" t="s">
+      <c r="H5" s="205" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="212" t="s">
+      <c r="I5" s="216" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="214" t="s">
+      <c r="J5" s="218" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="214" t="s">
+      <c r="K5" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="217" t="s">
+      <c r="L5" s="221" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="214" t="s">
+      <c r="M5" s="218" t="s">
         <v>286</v>
       </c>
-      <c r="N5" s="214" t="s">
+      <c r="N5" s="218" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="207"/>
-      <c r="B6" s="220"/>
-      <c r="C6" s="207"/>
-      <c r="D6" s="222"/>
-      <c r="E6" s="222"/>
-      <c r="F6" s="207"/>
-      <c r="G6" s="207"/>
-      <c r="H6" s="207"/>
-      <c r="I6" s="213"/>
-      <c r="J6" s="215"/>
-      <c r="K6" s="215"/>
-      <c r="L6" s="218"/>
-      <c r="M6" s="215"/>
-      <c r="N6" s="215"/>
-    </row>
-    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="207"/>
-      <c r="B7" s="220"/>
-      <c r="C7" s="207"/>
-      <c r="D7" s="222"/>
-      <c r="E7" s="222"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="207"/>
-      <c r="H7" s="207"/>
-      <c r="I7" s="213"/>
-      <c r="J7" s="215"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="218"/>
+    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="206"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="222"/>
+      <c r="M6" s="219"/>
+      <c r="N6" s="219"/>
+    </row>
+    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="206"/>
+      <c r="B7" s="208"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="210"/>
+      <c r="E7" s="210"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="219"/>
+      <c r="K7" s="220"/>
+      <c r="L7" s="222"/>
       <c r="M7" s="148" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/10</v>
@@ -5588,7 +5662,7 @@
         <v>VTO 15/10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>121</v>
       </c>
@@ -5635,12 +5709,12 @@
         <v>95837.855052240004</v>
       </c>
       <c r="O8" s="129"/>
-      <c r="Q8" s="205" t="s">
+      <c r="Q8" s="211" t="s">
         <v>259</v>
       </c>
-      <c r="R8" s="205"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R8" s="211"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="36" t="s">
@@ -5683,10 +5757,10 @@
         <v>113585.90156672</v>
       </c>
       <c r="O9" s="129"/>
-      <c r="Q9" s="205"/>
-      <c r="R9" s="205"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q9" s="211"/>
+      <c r="R9" s="211"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>121</v>
       </c>
@@ -5736,7 +5810,7 @@
         <v>90413.070804000003</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>121</v>
       </c>
@@ -5786,7 +5860,7 @@
         <v>107156.23206400001</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>121</v>
       </c>
@@ -5839,7 +5913,7 @@
         <v>101296.12562299999</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="61" t="s">
         <v>123</v>
       </c>
@@ -5896,7 +5970,7 @@
         <v>124736.55138700001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="61" t="s">
         <v>124</v>
       </c>
@@ -5954,7 +6028,7 @@
         <v>145665.502962</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="61" t="s">
         <v>123</v>
       </c>
@@ -6005,7 +6079,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="61" t="s">
         <v>125</v>
       </c>
@@ -6054,7 +6128,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="61" t="s">
         <v>125</v>
       </c>
@@ -6107,7 +6181,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="61" t="s">
         <v>125</v>
       </c>
@@ -6160,7 +6234,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="61" t="s">
         <v>123</v>
       </c>
@@ -6212,7 +6286,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="61" t="s">
         <v>124</v>
       </c>
@@ -6263,7 +6337,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="61" t="s">
         <v>123</v>
       </c>
@@ -6311,7 +6385,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="61" t="s">
         <v>125</v>
       </c>
@@ -6359,7 +6433,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="61" t="s">
         <v>125</v>
       </c>
@@ -6409,7 +6483,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="61" t="s">
         <v>125</v>
       </c>
@@ -6457,7 +6531,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="61" t="s">
         <v>123</v>
       </c>
@@ -6508,7 +6582,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="61" t="s">
         <v>124</v>
       </c>
@@ -6561,7 +6635,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="61" t="s">
         <v>123</v>
       </c>
@@ -6612,7 +6686,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="159" t="s">
         <v>125</v>
       </c>
@@ -6663,7 +6737,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="61" t="s">
         <v>125</v>
       </c>
@@ -6716,7 +6790,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="61" t="s">
         <v>125</v>
       </c>
@@ -6767,7 +6841,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="61" t="s">
         <v>123</v>
       </c>
@@ -6820,7 +6894,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="61" t="s">
         <v>124</v>
       </c>
@@ -6871,7 +6945,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="159" t="s">
         <v>123</v>
       </c>
@@ -6919,7 +6993,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="159" t="s">
         <v>125</v>
       </c>
@@ -6970,7 +7044,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="159" t="s">
         <v>125</v>
       </c>
@@ -7024,7 +7098,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" s="161" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="159" t="s">
         <v>125</v>
       </c>
@@ -7075,7 +7149,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="61" t="s">
         <v>123</v>
       </c>
@@ -7126,7 +7200,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="61" t="s">
         <v>124</v>
       </c>
@@ -7179,7 +7253,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="61" t="s">
         <v>123</v>
       </c>
@@ -7236,7 +7310,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="61" t="s">
         <v>125</v>
       </c>
@@ -7290,7 +7364,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="61" t="s">
         <v>125</v>
       </c>
@@ -7343,7 +7417,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="61" t="s">
         <v>125</v>
       </c>
@@ -7394,7 +7468,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="61" t="s">
         <v>123</v>
       </c>
@@ -7445,7 +7519,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="61" t="s">
         <v>124</v>
       </c>
@@ -7497,7 +7571,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="61" t="s">
         <v>123</v>
       </c>
@@ -7549,7 +7623,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="61" t="s">
         <v>125</v>
       </c>
@@ -7602,7 +7676,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="61" t="s">
         <v>125</v>
       </c>
@@ -7653,7 +7727,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="61" t="s">
         <v>125</v>
       </c>
@@ -7704,7 +7778,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="61" t="s">
         <v>123</v>
       </c>
@@ -7756,7 +7830,7 @@
       </c>
       <c r="Q49" s="63"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="61" t="s">
         <v>124</v>
       </c>
@@ -7809,7 +7883,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="61" t="s">
         <v>123</v>
       </c>
@@ -7860,7 +7934,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="61" t="s">
         <v>125</v>
       </c>
@@ -7910,7 +7984,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="61" t="s">
         <v>125</v>
       </c>
@@ -7964,7 +8038,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="61" t="s">
         <v>125</v>
       </c>
@@ -8018,7 +8092,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="61" t="s">
         <v>123</v>
       </c>
@@ -8069,7 +8143,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="61" t="s">
         <v>124</v>
       </c>
@@ -8120,7 +8194,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="61" t="s">
         <v>123</v>
       </c>
@@ -8171,7 +8245,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="61" t="s">
         <v>125</v>
       </c>
@@ -8224,7 +8298,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="61" t="s">
         <v>125</v>
       </c>
@@ -8275,7 +8349,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="61" t="s">
         <v>125</v>
       </c>
@@ -8326,7 +8400,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="61" t="s">
         <v>123</v>
       </c>
@@ -8377,7 +8451,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="159" t="s">
         <v>124</v>
       </c>
@@ -8425,7 +8499,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="61" t="s">
         <v>123</v>
       </c>
@@ -8476,7 +8550,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="61" t="s">
         <v>125</v>
       </c>
@@ -8526,7 +8600,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="61" t="s">
         <v>125</v>
       </c>
@@ -8580,7 +8654,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="61" t="s">
         <v>125</v>
       </c>
@@ -8631,7 +8705,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="61" t="s">
         <v>126</v>
       </c>
@@ -8682,7 +8756,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="61" t="s">
         <v>123</v>
       </c>
@@ -8732,7 +8806,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="61" t="s">
         <v>125</v>
       </c>
@@ -8783,7 +8857,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="61" t="s">
         <v>125</v>
       </c>
@@ -8836,7 +8910,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="61" t="s">
         <v>125</v>
       </c>
@@ -8886,7 +8960,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="61" t="s">
         <v>126</v>
       </c>
@@ -8934,7 +9008,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="61" t="s">
         <v>123</v>
       </c>
@@ -8985,7 +9059,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="61" t="s">
         <v>125</v>
       </c>
@@ -9036,7 +9110,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="61" t="s">
         <v>125</v>
       </c>
@@ -9089,7 +9163,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="61" t="s">
         <v>125</v>
       </c>
@@ -9143,7 +9217,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="61" t="s">
         <v>126</v>
       </c>
@@ -9194,7 +9268,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="61" t="s">
         <v>123</v>
       </c>
@@ -9245,7 +9319,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="61" t="s">
         <v>125</v>
       </c>
@@ -9296,7 +9370,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="61" t="s">
         <v>125</v>
       </c>
@@ -9347,7 +9421,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="122" t="s">
         <v>125</v>
       </c>
@@ -9398,7 +9472,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="122"/>
       <c r="B82" s="36"/>
       <c r="C82" s="36" t="s">
@@ -9447,7 +9521,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="122"/>
       <c r="B83" s="36"/>
       <c r="C83" s="36" t="s">
@@ -9496,7 +9570,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="122"/>
       <c r="B84" s="36"/>
       <c r="C84" s="36" t="s">
@@ -9544,7 +9618,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="122"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36" t="s">
@@ -9593,7 +9667,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="122"/>
       <c r="B86" s="36"/>
       <c r="C86" s="36" t="s">
@@ -9645,7 +9719,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="122"/>
       <c r="B87" s="36"/>
       <c r="C87" s="36" t="s">
@@ -9691,7 +9765,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="122"/>
       <c r="B88" s="36"/>
       <c r="C88" s="36" t="s">
@@ -9740,7 +9814,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="122"/>
       <c r="B89" s="36"/>
       <c r="C89" s="36" t="s">
@@ -9789,7 +9863,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="122"/>
       <c r="B90" s="36"/>
       <c r="C90" s="36" t="s">
@@ -9838,7 +9912,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="122"/>
       <c r="B91" s="36"/>
       <c r="C91" s="36" t="s">
@@ -9884,7 +9958,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="122"/>
       <c r="B92" s="36"/>
       <c r="C92" s="36" t="s">
@@ -9933,7 +10007,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="122"/>
       <c r="B93" s="36"/>
       <c r="C93" s="36" t="s">
@@ -9982,7 +10056,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="122"/>
       <c r="B94" s="36"/>
       <c r="C94" s="36" t="s">
@@ -10031,7 +10105,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="122"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36" t="s">
@@ -10080,7 +10154,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="122"/>
       <c r="B96" s="36"/>
       <c r="C96" s="36" t="s">
@@ -10129,7 +10203,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="122"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36" t="s">
@@ -10178,7 +10252,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="122"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
@@ -10227,7 +10301,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="122"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36" t="s">
@@ -10276,7 +10350,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="122"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36" t="s">
@@ -10324,7 +10398,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="122"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36" t="s">
@@ -10373,7 +10447,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="122"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36" t="s">
@@ -10422,7 +10496,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="122"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36" t="s">
@@ -10471,7 +10545,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="122"/>
       <c r="B104" s="36"/>
       <c r="C104" s="36" t="s">
@@ -10520,7 +10594,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="122"/>
       <c r="B105" s="36"/>
       <c r="C105" s="36" t="s">
@@ -10569,7 +10643,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="122"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36" t="s">
@@ -10618,7 +10692,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="122"/>
       <c r="B107" s="36"/>
       <c r="C107" s="36" t="s">
@@ -10667,7 +10741,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="122"/>
       <c r="B108" s="36"/>
       <c r="C108" s="36" t="s">
@@ -10715,7 +10789,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="122"/>
       <c r="B109" s="36"/>
       <c r="C109" s="36" t="s">
@@ -10764,7 +10838,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="122"/>
       <c r="B110" s="36"/>
       <c r="C110" s="36" t="s">
@@ -10810,7 +10884,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="122"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
@@ -10856,7 +10930,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="122"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
@@ -10908,7 +10982,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="143"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
@@ -10957,7 +11031,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="143"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
@@ -11006,7 +11080,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="143"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
@@ -11052,7 +11126,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="143"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
@@ -11101,7 +11175,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="143"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
@@ -11147,7 +11221,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="143"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
@@ -11193,7 +11267,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="143"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
@@ -11239,7 +11313,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="143"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
@@ -11285,7 +11359,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="143"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
@@ -11334,7 +11408,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="143"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
@@ -11382,7 +11456,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="143"/>
       <c r="B123" s="36"/>
       <c r="C123" s="36" t="s">
@@ -11431,7 +11505,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="143" t="s">
         <v>26</v>
       </c>
@@ -11482,7 +11556,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="143" t="s">
         <v>26</v>
       </c>
@@ -11533,7 +11607,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="56" t="s">
         <v>26</v>
       </c>
@@ -11551,7 +11625,7 @@
       <c r="M126" s="5"/>
       <c r="N126" s="9"/>
     </row>
-    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="28"/>
       <c r="B127" s="28"/>
       <c r="C127" s="28"/>
@@ -11592,41 +11666,41 @@
       </c>
       <c r="P127" s="63"/>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K128" s="65">
         <f>K127-L1</f>
         <v>-494947.15715999901</v>
       </c>
     </row>
-    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="209"/>
-      <c r="D129" s="209"/>
-      <c r="E129" s="209"/>
-      <c r="F129" s="209"/>
-      <c r="G129" s="209"/>
-      <c r="H129" s="209"/>
-      <c r="I129" s="209"/>
-      <c r="J129" s="209"/>
-      <c r="K129" s="209"/>
-      <c r="L129" s="209"/>
-      <c r="M129" s="209"/>
-      <c r="N129" s="209"/>
-    </row>
-    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="209"/>
-      <c r="D130" s="209"/>
-      <c r="E130" s="209"/>
-      <c r="F130" s="209"/>
-      <c r="G130" s="209"/>
-      <c r="H130" s="209"/>
-      <c r="I130" s="209"/>
-      <c r="J130" s="209"/>
-      <c r="K130" s="209"/>
-      <c r="L130" s="209"/>
-      <c r="M130" s="209"/>
-      <c r="N130" s="209"/>
-    </row>
-    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="213"/>
+      <c r="D129" s="213"/>
+      <c r="E129" s="213"/>
+      <c r="F129" s="213"/>
+      <c r="G129" s="213"/>
+      <c r="H129" s="213"/>
+      <c r="I129" s="213"/>
+      <c r="J129" s="213"/>
+      <c r="K129" s="213"/>
+      <c r="L129" s="213"/>
+      <c r="M129" s="213"/>
+      <c r="N129" s="213"/>
+    </row>
+    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="213"/>
+      <c r="D130" s="213"/>
+      <c r="E130" s="213"/>
+      <c r="F130" s="213"/>
+      <c r="G130" s="213"/>
+      <c r="H130" s="213"/>
+      <c r="I130" s="213"/>
+      <c r="J130" s="213"/>
+      <c r="K130" s="213"/>
+      <c r="L130" s="213"/>
+      <c r="M130" s="213"/>
+      <c r="N130" s="213"/>
+    </row>
+    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="86"/>
       <c r="D131" s="86"/>
       <c r="E131" s="86"/>
@@ -11640,121 +11714,121 @@
       <c r="M131" s="86"/>
       <c r="N131" s="86"/>
     </row>
-    <row r="132" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C132" s="209" t="s">
+    <row r="132" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C132" s="213" t="s">
         <v>265</v>
       </c>
-      <c r="D132" s="209"/>
-      <c r="E132" s="209"/>
-      <c r="F132" s="209"/>
-      <c r="G132" s="209"/>
-      <c r="H132" s="209"/>
-      <c r="I132" s="209"/>
-      <c r="J132" s="209"/>
-      <c r="K132" s="209"/>
-      <c r="L132" s="209"/>
-      <c r="M132" s="209"/>
-      <c r="N132" s="209"/>
-    </row>
-    <row r="133" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C133" s="209"/>
-      <c r="D133" s="209"/>
-      <c r="E133" s="209"/>
-      <c r="F133" s="209"/>
-      <c r="G133" s="209"/>
-      <c r="H133" s="209"/>
-      <c r="I133" s="209"/>
-      <c r="J133" s="209"/>
-      <c r="K133" s="209"/>
-      <c r="L133" s="209"/>
-      <c r="M133" s="209"/>
-      <c r="N133" s="209"/>
-    </row>
-    <row r="134" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C134" s="209"/>
-      <c r="D134" s="209"/>
-      <c r="E134" s="209"/>
-      <c r="F134" s="209"/>
-      <c r="G134" s="209"/>
-      <c r="H134" s="209"/>
-      <c r="I134" s="209"/>
-      <c r="J134" s="209"/>
-      <c r="K134" s="209"/>
-      <c r="L134" s="209"/>
-      <c r="M134" s="209"/>
-      <c r="N134" s="209"/>
-    </row>
-    <row r="135" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C135" s="209"/>
-      <c r="D135" s="209"/>
-      <c r="E135" s="209"/>
-      <c r="F135" s="209"/>
-      <c r="G135" s="209"/>
-      <c r="H135" s="209"/>
-      <c r="I135" s="209"/>
-      <c r="J135" s="209"/>
-      <c r="K135" s="209"/>
-      <c r="L135" s="209"/>
-      <c r="M135" s="209"/>
-      <c r="N135" s="209"/>
-    </row>
-    <row r="136" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C136" s="209"/>
-      <c r="D136" s="209"/>
-      <c r="E136" s="209"/>
-      <c r="F136" s="209"/>
-      <c r="G136" s="209"/>
-      <c r="H136" s="209"/>
-      <c r="I136" s="209"/>
-      <c r="J136" s="209"/>
-      <c r="K136" s="209"/>
-      <c r="L136" s="209"/>
-      <c r="M136" s="209"/>
-      <c r="N136" s="209"/>
-    </row>
-    <row r="137" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C137" s="209"/>
-      <c r="D137" s="209"/>
-      <c r="E137" s="209"/>
-      <c r="F137" s="209"/>
-      <c r="G137" s="209"/>
-      <c r="H137" s="209"/>
-      <c r="I137" s="209"/>
-      <c r="J137" s="209"/>
-      <c r="K137" s="209"/>
-      <c r="L137" s="209"/>
-      <c r="M137" s="209"/>
-      <c r="N137" s="209"/>
-    </row>
-    <row r="138" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="209"/>
-      <c r="D138" s="209"/>
-      <c r="E138" s="209"/>
-      <c r="F138" s="209"/>
-      <c r="G138" s="209"/>
-      <c r="H138" s="209"/>
-      <c r="I138" s="209"/>
-      <c r="J138" s="209"/>
-      <c r="K138" s="209"/>
-      <c r="L138" s="209"/>
-      <c r="M138" s="209"/>
-      <c r="N138" s="209"/>
-    </row>
-    <row r="139" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="209"/>
-      <c r="D139" s="209"/>
-      <c r="E139" s="209"/>
-      <c r="F139" s="209"/>
-      <c r="G139" s="209"/>
-      <c r="H139" s="209"/>
-      <c r="I139" s="209"/>
-      <c r="J139" s="209"/>
-      <c r="K139" s="209"/>
-      <c r="L139" s="209"/>
-      <c r="M139" s="209"/>
-      <c r="N139" s="209"/>
-    </row>
-    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="213"/>
+      <c r="E132" s="213"/>
+      <c r="F132" s="213"/>
+      <c r="G132" s="213"/>
+      <c r="H132" s="213"/>
+      <c r="I132" s="213"/>
+      <c r="J132" s="213"/>
+      <c r="K132" s="213"/>
+      <c r="L132" s="213"/>
+      <c r="M132" s="213"/>
+      <c r="N132" s="213"/>
+    </row>
+    <row r="133" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C133" s="213"/>
+      <c r="D133" s="213"/>
+      <c r="E133" s="213"/>
+      <c r="F133" s="213"/>
+      <c r="G133" s="213"/>
+      <c r="H133" s="213"/>
+      <c r="I133" s="213"/>
+      <c r="J133" s="213"/>
+      <c r="K133" s="213"/>
+      <c r="L133" s="213"/>
+      <c r="M133" s="213"/>
+      <c r="N133" s="213"/>
+    </row>
+    <row r="134" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C134" s="213"/>
+      <c r="D134" s="213"/>
+      <c r="E134" s="213"/>
+      <c r="F134" s="213"/>
+      <c r="G134" s="213"/>
+      <c r="H134" s="213"/>
+      <c r="I134" s="213"/>
+      <c r="J134" s="213"/>
+      <c r="K134" s="213"/>
+      <c r="L134" s="213"/>
+      <c r="M134" s="213"/>
+      <c r="N134" s="213"/>
+    </row>
+    <row r="135" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C135" s="213"/>
+      <c r="D135" s="213"/>
+      <c r="E135" s="213"/>
+      <c r="F135" s="213"/>
+      <c r="G135" s="213"/>
+      <c r="H135" s="213"/>
+      <c r="I135" s="213"/>
+      <c r="J135" s="213"/>
+      <c r="K135" s="213"/>
+      <c r="L135" s="213"/>
+      <c r="M135" s="213"/>
+      <c r="N135" s="213"/>
+    </row>
+    <row r="136" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C136" s="213"/>
+      <c r="D136" s="213"/>
+      <c r="E136" s="213"/>
+      <c r="F136" s="213"/>
+      <c r="G136" s="213"/>
+      <c r="H136" s="213"/>
+      <c r="I136" s="213"/>
+      <c r="J136" s="213"/>
+      <c r="K136" s="213"/>
+      <c r="L136" s="213"/>
+      <c r="M136" s="213"/>
+      <c r="N136" s="213"/>
+    </row>
+    <row r="137" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C137" s="213"/>
+      <c r="D137" s="213"/>
+      <c r="E137" s="213"/>
+      <c r="F137" s="213"/>
+      <c r="G137" s="213"/>
+      <c r="H137" s="213"/>
+      <c r="I137" s="213"/>
+      <c r="J137" s="213"/>
+      <c r="K137" s="213"/>
+      <c r="L137" s="213"/>
+      <c r="M137" s="213"/>
+      <c r="N137" s="213"/>
+    </row>
+    <row r="138" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="213"/>
+      <c r="D138" s="213"/>
+      <c r="E138" s="213"/>
+      <c r="F138" s="213"/>
+      <c r="G138" s="213"/>
+      <c r="H138" s="213"/>
+      <c r="I138" s="213"/>
+      <c r="J138" s="213"/>
+      <c r="K138" s="213"/>
+      <c r="L138" s="213"/>
+      <c r="M138" s="213"/>
+      <c r="N138" s="213"/>
+    </row>
+    <row r="139" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="213"/>
+      <c r="D139" s="213"/>
+      <c r="E139" s="213"/>
+      <c r="F139" s="213"/>
+      <c r="G139" s="213"/>
+      <c r="H139" s="213"/>
+      <c r="I139" s="213"/>
+      <c r="J139" s="213"/>
+      <c r="K139" s="213"/>
+      <c r="L139" s="213"/>
+      <c r="M139" s="213"/>
+      <c r="N139" s="213"/>
+    </row>
+    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="86"/>
       <c r="D140" s="86"/>
       <c r="E140" s="86"/>
@@ -11768,7 +11842,7 @@
       <c r="M140" s="86"/>
       <c r="N140" s="86"/>
     </row>
-    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="86"/>
       <c r="D141" s="86"/>
       <c r="E141" s="86"/>
@@ -11782,118 +11856,112 @@
       <c r="M141" s="86"/>
       <c r="N141" s="86"/>
     </row>
-    <row r="142" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="208" t="s">
+    <row r="142" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="212" t="s">
         <v>264</v>
       </c>
-      <c r="D142" s="208"/>
-      <c r="E142" s="208"/>
-      <c r="F142" s="208"/>
-      <c r="G142" s="208"/>
-      <c r="H142" s="208"/>
-      <c r="I142" s="208"/>
-      <c r="J142" s="208"/>
-      <c r="K142" s="208"/>
-      <c r="L142" s="208"/>
-      <c r="M142" s="208"/>
-      <c r="N142" s="208"/>
-    </row>
-    <row r="143" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="208"/>
-      <c r="D143" s="208"/>
-      <c r="E143" s="208"/>
-      <c r="F143" s="208"/>
-      <c r="G143" s="208"/>
-      <c r="H143" s="208"/>
-      <c r="I143" s="208"/>
-      <c r="J143" s="208"/>
-      <c r="K143" s="208"/>
-      <c r="L143" s="208"/>
-      <c r="M143" s="208"/>
-      <c r="N143" s="208"/>
-    </row>
-    <row r="144" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="208"/>
-      <c r="D144" s="208"/>
-      <c r="E144" s="208"/>
-      <c r="F144" s="208"/>
-      <c r="G144" s="208"/>
-      <c r="H144" s="208"/>
-      <c r="I144" s="208"/>
-      <c r="J144" s="208"/>
-      <c r="K144" s="208"/>
-      <c r="L144" s="208"/>
-      <c r="M144" s="208"/>
-      <c r="N144" s="208"/>
+      <c r="D142" s="212"/>
+      <c r="E142" s="212"/>
+      <c r="F142" s="212"/>
+      <c r="G142" s="212"/>
+      <c r="H142" s="212"/>
+      <c r="I142" s="212"/>
+      <c r="J142" s="212"/>
+      <c r="K142" s="212"/>
+      <c r="L142" s="212"/>
+      <c r="M142" s="212"/>
+      <c r="N142" s="212"/>
+    </row>
+    <row r="143" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="212"/>
+      <c r="D143" s="212"/>
+      <c r="E143" s="212"/>
+      <c r="F143" s="212"/>
+      <c r="G143" s="212"/>
+      <c r="H143" s="212"/>
+      <c r="I143" s="212"/>
+      <c r="J143" s="212"/>
+      <c r="K143" s="212"/>
+      <c r="L143" s="212"/>
+      <c r="M143" s="212"/>
+      <c r="N143" s="212"/>
+    </row>
+    <row r="144" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="212"/>
+      <c r="D144" s="212"/>
+      <c r="E144" s="212"/>
+      <c r="F144" s="212"/>
+      <c r="G144" s="212"/>
+      <c r="H144" s="212"/>
+      <c r="I144" s="212"/>
+      <c r="J144" s="212"/>
+      <c r="K144" s="212"/>
+      <c r="L144" s="212"/>
+      <c r="M144" s="212"/>
+      <c r="N144" s="212"/>
       <c r="P144" s="94">
         <f>L1-K127</f>
         <v>494947.15715999901</v>
       </c>
     </row>
-    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="208"/>
-      <c r="D145" s="208"/>
-      <c r="E145" s="208"/>
-      <c r="F145" s="208"/>
-      <c r="G145" s="208"/>
-      <c r="H145" s="208"/>
-      <c r="I145" s="208"/>
-      <c r="J145" s="208"/>
-      <c r="K145" s="208"/>
-      <c r="L145" s="208"/>
-      <c r="M145" s="208"/>
-      <c r="N145" s="208"/>
-    </row>
-    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="208"/>
-      <c r="D146" s="208"/>
-      <c r="E146" s="208"/>
-      <c r="F146" s="208"/>
-      <c r="G146" s="208"/>
-      <c r="H146" s="208"/>
-      <c r="I146" s="208"/>
-      <c r="J146" s="208"/>
-      <c r="K146" s="208"/>
-      <c r="L146" s="208"/>
-      <c r="M146" s="208"/>
-      <c r="N146" s="208"/>
-    </row>
-    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="208"/>
-      <c r="D147" s="208"/>
-      <c r="E147" s="208"/>
-      <c r="F147" s="208"/>
-      <c r="G147" s="208"/>
-      <c r="H147" s="208"/>
-      <c r="I147" s="208"/>
-      <c r="J147" s="208"/>
-      <c r="K147" s="208"/>
-      <c r="L147" s="208"/>
-      <c r="M147" s="208"/>
-      <c r="N147" s="208"/>
-    </row>
-    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="208"/>
-      <c r="D148" s="208"/>
-      <c r="E148" s="208"/>
-      <c r="F148" s="208"/>
-      <c r="G148" s="208"/>
-      <c r="H148" s="208"/>
-      <c r="I148" s="208"/>
-      <c r="J148" s="208"/>
-      <c r="K148" s="208"/>
-      <c r="L148" s="208"/>
-      <c r="M148" s="208"/>
-      <c r="N148" s="208"/>
+    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="212"/>
+      <c r="D145" s="212"/>
+      <c r="E145" s="212"/>
+      <c r="F145" s="212"/>
+      <c r="G145" s="212"/>
+      <c r="H145" s="212"/>
+      <c r="I145" s="212"/>
+      <c r="J145" s="212"/>
+      <c r="K145" s="212"/>
+      <c r="L145" s="212"/>
+      <c r="M145" s="212"/>
+      <c r="N145" s="212"/>
+    </row>
+    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="212"/>
+      <c r="D146" s="212"/>
+      <c r="E146" s="212"/>
+      <c r="F146" s="212"/>
+      <c r="G146" s="212"/>
+      <c r="H146" s="212"/>
+      <c r="I146" s="212"/>
+      <c r="J146" s="212"/>
+      <c r="K146" s="212"/>
+      <c r="L146" s="212"/>
+      <c r="M146" s="212"/>
+      <c r="N146" s="212"/>
+    </row>
+    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="212"/>
+      <c r="D147" s="212"/>
+      <c r="E147" s="212"/>
+      <c r="F147" s="212"/>
+      <c r="G147" s="212"/>
+      <c r="H147" s="212"/>
+      <c r="I147" s="212"/>
+      <c r="J147" s="212"/>
+      <c r="K147" s="212"/>
+      <c r="L147" s="212"/>
+      <c r="M147" s="212"/>
+      <c r="N147" s="212"/>
+    </row>
+    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="212"/>
+      <c r="D148" s="212"/>
+      <c r="E148" s="212"/>
+      <c r="F148" s="212"/>
+      <c r="G148" s="212"/>
+      <c r="H148" s="212"/>
+      <c r="I148" s="212"/>
+      <c r="J148" s="212"/>
+      <c r="K148" s="212"/>
+      <c r="L148" s="212"/>
+      <c r="M148" s="212"/>
+      <c r="N148" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C142:N148"/>
@@ -11907,6 +11975,12 @@
     <mergeCell ref="C132:N139"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11918,9 +11992,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="155"/>
     </row>
   </sheetData>
@@ -11929,20 +12003,331 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C328FACD-8136-4CA4-B080-DAA47D3374DA}">
+  <dimension ref="A2:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="224" t="str">
+        <f>RESUMEN!C5</f>
+        <v>PERÍODO: SEPTIEMBRE</v>
+      </c>
+      <c r="D3" s="225"/>
+      <c r="E3" s="225"/>
+      <c r="F3" s="225" t="str">
+        <f>[1]RESUMEN!A22</f>
+        <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+      </c>
+      <c r="G3" s="225"/>
+      <c r="H3" s="225"/>
+      <c r="I3" s="225"/>
+      <c r="J3" s="226"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+      <c r="J4" s="227"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="str">
+        <f>RESUMEN!A26</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G5" s="44">
+        <f>RESUMEN!D26</f>
+        <v>1008894</v>
+      </c>
+      <c r="H5" s="228" t="s">
+        <v>351</v>
+      </c>
+      <c r="I5" s="228"/>
+      <c r="J5" s="229"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="str">
+        <f>RESUMEN!A27</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G6" s="44">
+        <f>RESUMEN!D27</f>
+        <v>35211</v>
+      </c>
+      <c r="H6" s="228" t="s">
+        <v>352</v>
+      </c>
+      <c r="I6" s="228"/>
+      <c r="J6" s="229"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="str">
+        <f>RESUMEN!A28</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G7" s="44">
+        <f>RESUMEN!D28</f>
+        <v>122704</v>
+      </c>
+      <c r="H7" s="228"/>
+      <c r="I7" s="228"/>
+      <c r="J7" s="229"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="str">
+        <f>RESUMEN!A29</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G8" s="44">
+        <f>RESUMEN!D29</f>
+        <v>20931</v>
+      </c>
+      <c r="J8" s="227"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="str">
+        <f>RESUMEN!A30</f>
+        <v>Adicional Viaticos</v>
+      </c>
+      <c r="G9" s="44">
+        <f>RESUMEN!D30</f>
+        <v>58852.2</v>
+      </c>
+      <c r="H9" s="228" t="s">
+        <v>353</v>
+      </c>
+      <c r="I9" s="228"/>
+      <c r="J9" s="229"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="str">
+        <f>RESUMEN!A31</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G10" s="44">
+        <f>RESUMEN!D31</f>
+        <v>50000</v>
+      </c>
+      <c r="H10" s="228" t="s">
+        <v>352</v>
+      </c>
+      <c r="I10" s="228"/>
+      <c r="J10" s="229"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="H11" s="228"/>
+      <c r="I11" s="228"/>
+      <c r="J11" s="229"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="230" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="231">
+        <f>SUM(G5:G11)</f>
+        <v>1296592.2</v>
+      </c>
+      <c r="J12" s="227"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="232"/>
+      <c r="D13" s="233"/>
+      <c r="E13" s="233"/>
+      <c r="F13" s="233"/>
+      <c r="G13" s="233"/>
+      <c r="H13" s="233"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="234"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="224" t="str">
+        <f>C3</f>
+        <v>PERÍODO: SEPTIEMBRE</v>
+      </c>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225" t="str">
+        <f>[1]RESUMEN!A30</f>
+        <v>Sueldo encargada Miriam</v>
+      </c>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="226"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="J17" s="227"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="228" t="s">
+        <v>351</v>
+      </c>
+      <c r="I18" s="228"/>
+      <c r="J18" s="229"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="str">
+        <f>RESUMEN!A34</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G19" s="44">
+        <f>RESUMEN!D34</f>
+        <v>504447</v>
+      </c>
+      <c r="H19" s="228" t="s">
+        <v>352</v>
+      </c>
+      <c r="I19" s="228"/>
+      <c r="J19" s="229"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="str">
+        <f>RESUMEN!A35</f>
+        <v>Horas extras</v>
+      </c>
+      <c r="G20" s="44">
+        <f>RESUMEN!D35</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="228"/>
+      <c r="I20" s="228"/>
+      <c r="J20" s="229"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="str">
+        <f>RESUMEN!A36</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G21" s="44">
+        <f>RESUMEN!D36</f>
+        <v>35211</v>
+      </c>
+      <c r="J21" s="227"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="str">
+        <f>RESUMEN!A37</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G22" s="44">
+        <f>RESUMEN!D37</f>
+        <v>122704</v>
+      </c>
+      <c r="H22" s="228" t="s">
+        <v>353</v>
+      </c>
+      <c r="I22" s="228"/>
+      <c r="J22" s="229"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="str">
+        <f>RESUMEN!A38</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G23" s="44">
+        <f>RESUMEN!D38</f>
+        <v>20931</v>
+      </c>
+      <c r="H23" s="228" t="s">
+        <v>352</v>
+      </c>
+      <c r="I23" s="228"/>
+      <c r="J23" s="229"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="1" t="str">
+        <f>RESUMEN!A39</f>
+        <v>Adicional Viaticos</v>
+      </c>
+      <c r="G24" s="44">
+        <f>RESUMEN!D39</f>
+        <v>58852.2</v>
+      </c>
+      <c r="H24" s="228"/>
+      <c r="I24" s="228"/>
+      <c r="J24" s="229"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="1" t="str">
+        <f>RESUMEN!A40</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G25" s="44">
+        <f>RESUMEN!D40</f>
+        <v>50000</v>
+      </c>
+      <c r="H25" s="235"/>
+      <c r="I25" s="235"/>
+      <c r="J25" s="236"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="230" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="231">
+        <f>SUM(G18:G25)</f>
+        <v>792145.2</v>
+      </c>
+      <c r="J26" s="227"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="232"/>
+      <c r="D27" s="233"/>
+      <c r="E27" s="233"/>
+      <c r="F27" s="233"/>
+      <c r="G27" s="233"/>
+      <c r="H27" s="233"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="234"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J24"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J7"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="H10:J11"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C4" s="223" t="s">
         <v>288</v>
       </c>
       <c r="D4" s="223"/>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="153">
         <v>52141.08</v>
       </c>
@@ -11950,7 +12335,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="153">
         <v>67140.100000000006</v>
       </c>
@@ -11958,7 +12343,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="153">
         <v>52121.11</v>
       </c>
@@ -11966,7 +12351,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="153">
         <v>67885.119999999995</v>
       </c>
@@ -11974,7 +12359,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="153">
         <v>67140.160000000003</v>
       </c>
@@ -11982,7 +12367,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="153">
         <v>62141.17</v>
       </c>
@@ -11990,7 +12375,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="153">
         <v>67855.179999999993</v>
       </c>
@@ -11998,7 +12383,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="153">
         <v>62141.23</v>
       </c>
@@ -12006,7 +12391,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="153">
         <v>67855.240000000005</v>
       </c>
@@ -12014,7 +12399,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="153">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>
